--- a/data/export/2026-10-25-浦东35路.xlsx
+++ b/data/export/2026-10-25-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1603,1117 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东35路.xlsx
+++ b/data/export/2026-10-25-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AC28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>3/25</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -887,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +953,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -998,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1064,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1092,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>119分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1109,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,17 +1153,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1153,13 +1173,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>119.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1244,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1294,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1405,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1466,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1516,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1577,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1627,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1688,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1738,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1799,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1849,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1910,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1960,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2021,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2071,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2132,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2182,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2243,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2293,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2354,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2404,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2465,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2515,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2576,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2626,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2687,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2737,903 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>3/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>2/25</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东35路.xlsx
+++ b/data/export/2026-10-25-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -870,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -903,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -927,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -947,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1064,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1102,24 +1110,24 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>119分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1129,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1168,22 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1294,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1405,7 +1413,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1516,7 +1524,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1627,7 +1635,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1738,7 +1746,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1807,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1849,7 +1857,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1918,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1960,7 +1968,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2029,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2071,7 +2079,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2140,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2182,7 +2190,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2251,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2293,7 +2301,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2362,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2404,7 +2412,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2473,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2515,7 +2523,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2584,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2626,7 +2634,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2695,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2737,7 +2745,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2806,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2848,7 +2856,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2917,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2959,7 +2967,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3028,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3070,7 +3078,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3139,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3181,7 +3189,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3250,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3292,7 +3300,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3361,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3403,7 +3411,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3472,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3518,7 +3526,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3587,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3633,7 +3641,233 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>2/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>1/26</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东35路.xlsx
+++ b/data/export/2026-10-25-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC30"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>127.0</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -989,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1022,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -1110,24 +1118,24 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1137,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1186,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1252,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1276,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -1330,32 +1346,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1363,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1387,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1513,7 +1537,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1524,7 +1548,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1552,32 +1576,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1585,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1609,33 +1637,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -1663,32 +1695,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1696,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1720,17 +1756,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1740,13 +1776,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -1774,32 +1814,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1807,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1831,33 +1875,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>120.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -1885,32 +1933,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -1918,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1942,33 +1994,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -1996,32 +2052,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>116分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2029,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2053,17 +2113,17 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2073,13 +2133,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>116.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -2107,32 +2171,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2140,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2164,17 +2232,17 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -2184,13 +2252,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2301,7 +2373,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2412,7 +2484,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2523,7 +2595,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2634,7 +2706,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2767,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2745,7 +2817,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2878,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2856,7 +2928,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2989,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2967,7 +3039,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3100,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3078,7 +3150,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3211,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3189,7 +3261,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3322,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3300,7 +3372,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3433,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3411,7 +3483,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3544,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3526,7 +3598,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3659,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3641,7 +3713,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3774,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3752,7 +3824,7 @@
       <c r="AB29" s="2" t="inlineStr"/>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3760,22 +3832,22 @@
       <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3813,7 +3885,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3862,12 +3934,1039 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>6/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>12/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>10/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>13/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>120.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>10/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东35路.xlsx
+++ b/data/export/2026-10-25-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2181,24 +2181,24 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,22 +2247,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2401,32 +2401,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -2434,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2458,33 +2462,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -2512,32 +2520,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2545,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2569,33 +2581,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -2623,32 +2639,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2656,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2680,33 +2700,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2806,7 +2830,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2845,32 +2869,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -2878,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2902,17 +2930,17 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2922,13 +2950,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -2956,32 +2988,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2989,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3013,17 +3049,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3033,13 +3069,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -3067,32 +3107,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3100,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3124,33 +3168,37 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -3178,32 +3226,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3211,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3235,17 +3287,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3255,13 +3307,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>20/27</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3659,7 +3715,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3774,7 +3830,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,7 +3941,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4000,7 +4056,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4115,7 +4171,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4169,7 +4225,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4286,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4284,7 +4340,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4401,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4399,7 +4455,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4516,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4575,7 +4631,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4686,7 +4742,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4797,7 +4853,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4859,22 +4915,22 @@
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -4907,12 +4963,12 @@
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4961,12 +5017,1039 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
           <t>128.0</t>
         </is>
       </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>10/27</t>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>11/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>116.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>19/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>16/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>11/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东35路.xlsx
+++ b/data/export/2026-10-25-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -446,10 +446,10 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,14 +2945,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -3248,12 +3248,12 @@
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3345,32 +3345,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3378,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3402,17 +3406,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3422,13 +3426,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>21/27</t>
         </is>
       </c>
     </row>
@@ -3456,32 +3464,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3489,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3513,33 +3525,37 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>21/27</t>
         </is>
       </c>
     </row>
@@ -3567,32 +3583,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3600,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3624,37 +3644,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -3682,32 +3702,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3715,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3739,17 +3763,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3759,17 +3783,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3869,7 +3893,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3908,32 +3932,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3941,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3965,17 +3993,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -3985,17 +4013,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -4023,32 +4051,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4056,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4080,37 +4112,37 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -4138,32 +4170,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4171,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4195,17 +4231,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4215,17 +4251,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -4253,32 +4289,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4286,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4310,37 +4350,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -4401,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4440,7 +4480,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4455,7 +4495,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4556,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4598,12 +4638,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq48，推进10站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4631,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4639,10 +4679,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
           <t>09:38</t>
@@ -4742,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,7 +4909,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4968,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5022,7 +5078,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5139,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5137,7 +5193,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5313,7 +5369,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5367,7 +5423,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5484,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5539,7 +5595,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5593,7 +5649,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5710,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5769,7 +5825,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5880,7 +5936,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5934,7 +5990,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -5942,22 +5998,22 @@
       <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -5995,7 +6051,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6009,47 +6065,848 @@
       <c r="T48" s="2" t="inlineStr"/>
       <c r="U48" s="2" t="inlineStr">
         <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
           <t>11:16</t>
         </is>
       </c>
-      <c r="V48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W48" s="2" t="inlineStr">
+      <c r="W49" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X48" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y48" s="2" t="inlineStr">
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z48" s="2" t="inlineStr">
+      <c r="Z49" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
+      <c r="AA49" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB48" s="2" t="inlineStr">
+      <c r="AB49" s="2" t="inlineStr">
         <is>
           <t>127.0</t>
         </is>
       </c>
-      <c r="AC48" s="2" t="inlineStr">
-        <is>
-          <t>6/27</t>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>5/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>21/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>13/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>11/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>13/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>15/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东35路.xlsx
+++ b/data/export/2026-10-25-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,18 +1537,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1899,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2014,17 +2018,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,22 +2132,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,17 +2256,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2367,13 +2371,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,7 +2485,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2492,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2609,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2730,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2841,7 +2849,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2960,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3198,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>21/27</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3555,7 +3563,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>21/27</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3674,7 +3682,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3793,7 +3801,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3904,7 +3912,7 @@
       <c r="AB29" s="2" t="inlineStr"/>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4142,7 +4150,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4380,7 +4388,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4408,32 +4416,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4441,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4465,17 +4477,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4485,17 +4497,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4523,32 +4535,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4556,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4580,17 +4596,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4600,17 +4616,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4659,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq48，推进10站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq57，推进19站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4671,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4726,7 +4742,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4737,7 +4753,7 @@
       <c r="AB36" s="2" t="inlineStr"/>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4765,32 +4781,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4798,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4822,33 +4842,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB37" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4876,32 +4900,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4909,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4933,17 +4961,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4953,17 +4981,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4991,32 +5019,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5024,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5048,17 +5080,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5068,17 +5100,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5106,32 +5138,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5139,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5163,17 +5199,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5183,17 +5219,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5221,32 +5257,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5254,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5278,37 +5318,37 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5336,32 +5376,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5369,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5393,17 +5437,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5413,17 +5457,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5451,32 +5495,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5484,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5508,17 +5556,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5528,13 +5576,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5562,32 +5614,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -5595,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5619,17 +5675,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5639,17 +5695,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5749,7 +5805,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5764,7 +5820,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5825,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5875,7 +5931,7 @@
       <c r="AB46" s="2" t="inlineStr"/>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5990,7 +6046,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6051,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6105,7 +6161,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6222,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6220,7 +6276,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6281,7 +6337,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6335,7 +6391,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>21/27</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6452,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6450,7 +6506,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6511,7 +6567,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6561,7 +6617,7 @@
       <c r="AB52" s="2" t="inlineStr"/>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6678,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6676,7 +6732,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6737,7 +6793,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6791,7 +6847,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6908,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6896,17 +6952,695 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB55" s="2" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>15/27</t>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东35路.xlsx
+++ b/data/export/2026-10-25-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,17 +2251,17 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2728,17 +2728,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,18 +2838,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,22 +2957,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3196,17 +3200,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3548,7 +3552,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3563,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3667,22 +3671,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4031,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4150,7 +4154,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4388,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4507,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4818,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4872,7 +4876,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5114,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5348,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5386,24 +5390,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5413,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5452,17 +5456,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5505,12 +5509,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -5532,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5581,12 +5585,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5624,12 +5628,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -5651,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5700,12 +5704,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5733,32 +5737,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5766,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5790,17 +5798,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5810,17 +5818,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5848,32 +5856,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5881,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5905,33 +5917,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5959,32 +5975,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5992,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6016,17 +6036,17 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -6036,17 +6056,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6074,32 +6094,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6107,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6131,37 +6155,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6189,32 +6213,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6222,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6246,17 +6274,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6266,17 +6294,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6376,7 +6404,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6391,7 +6419,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -6419,32 +6447,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6452,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6476,37 +6508,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6678,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6732,7 +6764,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6793,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6847,7 +6879,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6962,7 +6994,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7134,7 +7166,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7188,7 +7220,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7281,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7360,7 +7392,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7414,7 +7446,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7475,7 +7507,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7586,7 +7618,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7630,17 +7662,592 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr">
-        <is>
-          <t>1/29</t>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>129.3</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东35路.xlsx
+++ b/data/export/2026-10-25-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC66"/>
+  <dimension ref="A1:AC70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>131.0</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,14 +3790,14 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>131.0</t>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3910,13 +3910,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4139,22 +4143,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4382,12 +4386,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4457,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,22 +4500,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4822,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5114,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5417,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5471,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5828,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5947,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6104,24 +6108,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6131,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6180,7 +6184,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6223,24 +6227,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6250,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6299,12 +6303,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6457,24 +6461,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6484,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6533,12 +6537,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6566,32 +6570,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -6599,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6623,17 +6631,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6643,13 +6651,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB52" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -6677,32 +6689,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6710,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6734,37 +6750,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6792,32 +6808,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6825,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6849,17 +6869,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6869,12 +6889,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6907,32 +6927,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -6940,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6964,37 +6988,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -7022,12 +7046,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq40，推进2站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7055,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7063,10 +7087,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q56" s="2" t="inlineStr"/>
-      <c r="R56" s="2" t="inlineStr"/>
-      <c r="S56" s="2" t="inlineStr"/>
-      <c r="T56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
           <t>12:28</t>
@@ -7166,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7281,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7392,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7507,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7618,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7672,7 +7712,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7733,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7787,7 +7827,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -7848,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7897,7 +7937,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7963,7 +8003,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8017,7 +8057,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8118,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8127,12 +8167,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -8193,7 +8233,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8251,6 +8291,466 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>131.7</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>133.3</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-25-浦东35路.xlsx
+++ b/data/export/2026-10-25-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC70"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,14 +1303,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1666,12 +1666,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4262,14 +4262,14 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4391,12 +4391,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6818,12 +6818,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6937,12 +6937,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq40，推进2站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq51，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -7288,32 +7288,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7321,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7345,33 +7349,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7547,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7658,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7712,7 +7720,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7781,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7827,7 +7835,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7942,7 +7950,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8057,7 +8065,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8172,7 +8180,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8287,7 +8295,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8356,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8402,7 +8410,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8471,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8517,7 +8525,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8586,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8632,7 +8640,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -8693,7 +8701,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8742,12 +8750,242 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东35路.xlsx
+++ b/data/export/2026-10-25-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,14 +1894,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>125.5</t>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,14 +2013,14 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>127.0</t>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2256,17 +2256,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2962,17 +2962,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,14 +3433,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>144.0</t>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>28/29</t>
         </is>
       </c>
     </row>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4870,17 +4870,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4984,14 +4984,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>125.5</t>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5222,14 +5222,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>127.0</t>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5346,17 +5346,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5465,17 +5465,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5822,17 +5822,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6179,17 +6179,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>28/29</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq51，推进13站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq60，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7173,32 +7173,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -7206,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7230,17 +7234,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7250,17 +7254,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7379,7 +7383,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -7407,32 +7411,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7440,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7464,17 +7472,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7484,17 +7492,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7522,32 +7530,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -7555,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7579,17 +7591,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7599,13 +7611,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -7633,32 +7649,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7666,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7690,17 +7710,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7710,17 +7730,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -7748,32 +7768,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7781,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7805,17 +7829,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7825,17 +7849,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7863,32 +7887,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7896,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7920,17 +7948,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7940,17 +7968,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8126,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8180,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8295,7 +8323,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8410,7 +8438,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8499,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8586,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8701,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8755,7 +8783,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8816,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8878,22 +8906,22 @@
       <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8926,12 +8954,12 @@
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8945,47 +8973,618 @@
       <c r="T72" s="2" t="inlineStr"/>
       <c r="U72" s="2" t="inlineStr">
         <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
           <t>15:25</t>
         </is>
       </c>
-      <c r="V72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W72" s="2" t="inlineStr">
+      <c r="W73" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X72" s="2" t="inlineStr">
+      <c r="X73" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y72" s="2" t="inlineStr">
+      <c r="Y73" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z72" s="2" t="inlineStr">
+      <c r="Z73" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
+      <c r="AA73" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
+      <c r="AB73" s="2" t="inlineStr">
         <is>
           <t>127.0</t>
         </is>
       </c>
-      <c r="AC72" s="2" t="inlineStr">
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>125.5</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
         <is>
           <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>26/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东35路.xlsx
+++ b/data/export/2026-10-25-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC77"/>
+  <dimension ref="A1:AC85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>132.5</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3557,17 +3557,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4024,14 +4024,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>132.5</t>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4148,17 +4148,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5470,12 +5470,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5941,17 +5941,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6413,17 +6413,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6770,17 +6770,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -7778,24 +7778,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8006,32 +8006,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -8039,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8063,17 +8067,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8083,17 +8087,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8121,32 +8125,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8154,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8178,17 +8186,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8198,12 +8206,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8236,32 +8244,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8269,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8293,17 +8305,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8313,17 +8325,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8438,7 +8450,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8466,32 +8478,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8499,7 +8515,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8523,17 +8539,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8543,17 +8559,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8729,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8783,7 +8799,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8860,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8898,7 +8914,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9070,7 +9086,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9185,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9300,7 +9316,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9415,7 +9431,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9469,7 +9485,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -9530,7 +9546,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9588,6 +9604,926 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>28/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>131.3</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-25-浦东35路.xlsx
+++ b/data/export/2026-10-25-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC85"/>
+  <dimension ref="A1:AC93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,14 +2132,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>128.7</t>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4262,22 +4262,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4505,17 +4505,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4989,17 +4989,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5341,14 +5341,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>128.7</t>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7008,17 +7008,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7249,7 +7249,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7487,14 +7487,14 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
           <t>128.7</t>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -8363,32 +8363,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8396,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8420,37 +8424,37 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -8488,24 +8492,24 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8515,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8564,7 +8568,7 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>133.2</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8630,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8669,7 +8673,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8684,7 +8688,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -8712,32 +8716,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -8745,7 +8753,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8769,17 +8777,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8789,17 +8797,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8827,32 +8835,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8860,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8884,37 +8896,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8942,12 +8954,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq37推进至seq56，推进19站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -8975,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8983,10 +8995,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q72" s="2" t="inlineStr"/>
-      <c r="R72" s="2" t="inlineStr"/>
-      <c r="S72" s="2" t="inlineStr"/>
-      <c r="T72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置浦建路锦绣路 ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
           <t>15:22</t>
@@ -9086,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9125,7 +9153,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9140,7 +9168,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -9168,32 +9196,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9201,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9225,17 +9257,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9245,17 +9277,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -9316,7 +9348,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9370,7 +9402,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9546,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9600,7 +9632,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9776,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9830,7 +9862,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -9891,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10006,7 +10038,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10060,7 +10092,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -10121,7 +10153,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10236,7 +10268,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10351,7 +10383,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10405,7 +10437,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10498,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10520,7 +10552,927 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>128.7</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>26/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>132.7</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>132.3</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东35路.xlsx
+++ b/data/export/2026-10-25-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC93"/>
+  <dimension ref="A1:AC101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,22 +1894,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2018,17 +2018,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2609,17 +2609,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,14 +2723,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3076,22 +3076,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3195,22 +3195,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,14 +3433,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>144.0</t>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>28/29</t>
+          <t>28/30</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       <c r="AB36" s="2" t="inlineStr"/>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4984,22 +4984,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5227,17 +5227,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5703,17 +5703,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6055,14 +6055,14 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6293,22 +6293,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>28/29</t>
+          <t>28/30</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       <c r="AB56" s="2" t="inlineStr"/>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7373,17 +7373,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7611,17 +7611,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9053,7 +9053,7 @@
       <c r="AB72" s="2" t="inlineStr"/>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -9081,32 +9081,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9114,7 +9118,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9138,17 +9142,17 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9158,17 +9162,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -9206,24 +9210,24 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9233,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9272,22 +9276,22 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -9315,32 +9319,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9348,7 +9356,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9372,37 +9380,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -9430,32 +9438,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9463,7 +9475,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9487,29 +9499,29 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
           <t>144.0</t>
@@ -9517,7 +9529,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -9545,32 +9557,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9578,7 +9594,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9602,17 +9618,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9622,17 +9638,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -9660,32 +9676,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -9693,7 +9713,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9717,17 +9737,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9737,17 +9757,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9795,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9808,7 +9832,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9832,17 +9856,17 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -9852,17 +9876,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9923,7 +9947,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9962,7 +9986,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -9977,7 +10001,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10005,32 +10029,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10038,7 +10066,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10062,37 +10090,37 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10181,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10207,7 +10235,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>28/29</t>
+          <t>28/30</t>
         </is>
       </c>
     </row>
@@ -10268,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10322,7 +10350,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -10383,7 +10411,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10437,7 +10465,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10526,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10552,7 +10580,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10641,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10667,7 +10695,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10728,7 +10756,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10782,7 +10810,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -10843,7 +10871,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10897,7 +10925,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -10958,7 +10986,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11012,7 +11040,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -11073,7 +11101,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11127,7 +11155,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11216,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11242,7 +11270,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -11303,7 +11331,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11357,7 +11385,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -11418,7 +11446,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11462,17 +11490,929 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr"/>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB93" s="2" t="inlineStr">
-        <is>
-          <t>127.0</t>
-        </is>
-      </c>
-      <c r="AC93" s="2" t="inlineStr">
-        <is>
-          <t>3/29</t>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr"/>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>27/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>129.3</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东35路.xlsx
+++ b/data/export/2026-10-25-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC101"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3319,17 +3319,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>28/30</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>28/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4029,12 +4029,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4386,17 +4386,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4619,22 +4619,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6646,22 +6646,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>28/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6889,17 +6889,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7606,14 +7606,14 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
           <t>125.5</t>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8444,17 +8444,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>28/30</t>
         </is>
       </c>
     </row>
@@ -9594,7 +9594,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9752,14 +9752,14 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
           <t>125.5</t>
@@ -9767,7 +9767,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -9832,7 +9832,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9914,32 +9914,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9947,7 +9951,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9971,17 +9975,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9991,12 +9995,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10039,12 +10043,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
@@ -10066,7 +10070,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10115,12 +10119,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -10148,32 +10152,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -10181,7 +10189,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10205,37 +10213,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>28/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -10263,32 +10271,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -10296,7 +10308,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10320,37 +10332,37 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -10378,32 +10390,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10411,7 +10427,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10435,17 +10451,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10455,7 +10471,7 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
@@ -10493,32 +10509,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10526,7 +10546,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10550,17 +10570,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10570,17 +10590,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>133.2</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -10641,7 +10661,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10695,7 +10715,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -10723,32 +10743,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10756,7 +10780,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10780,17 +10804,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10800,17 +10824,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -10871,7 +10895,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10986,7 +11010,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11101,7 +11125,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11216,7 +11240,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11270,7 +11294,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -11331,7 +11355,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11385,7 +11409,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11470,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11500,7 +11524,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11585,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11672,7 +11696,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11726,7 +11750,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -11787,7 +11811,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11902,7 +11926,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12013,7 +12037,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12067,7 +12091,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>28/30</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12152,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12243,7 +12267,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12292,12 +12316,12 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -12358,7 +12382,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12402,17 +12426,592 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>132.7</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>130.7</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>8/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB101" s="2" t="inlineStr">
-        <is>
-          <t>132.5</t>
-        </is>
-      </c>
-      <c r="AC101" s="2" t="inlineStr">
-        <is>
-          <t>16/30</t>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>125.5</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>27/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>133.7</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东35路.xlsx
+++ b/data/export/2026-10-25-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC106"/>
+  <dimension ref="A1:AC107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2371,17 +2371,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4870,17 +4870,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5584,17 +5584,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7254,17 +7254,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10628,32 +10628,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10661,7 +10665,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10685,17 +10689,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10705,17 +10709,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -10780,7 +10784,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10895,7 +10899,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10977,32 +10981,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11010,7 +11018,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11034,17 +11042,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11054,17 +11062,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -11125,7 +11133,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11240,7 +11248,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11294,7 +11302,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11363,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11409,7 +11417,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -11470,7 +11478,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11524,7 +11532,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -11585,7 +11593,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11696,7 +11704,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11811,7 +11819,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11926,7 +11934,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12037,7 +12045,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12152,7 +12160,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12267,7 +12275,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12382,7 +12390,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12436,7 +12444,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -12497,7 +12505,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12612,7 +12620,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12727,7 +12735,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12842,7 +12850,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12957,7 +12965,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13015,6 +13023,121 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>5/30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-25-浦东35路.xlsx
+++ b/data/export/2026-10-25-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC107"/>
+  <dimension ref="A1:AC110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3795,17 +3795,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4267,17 +4267,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5346,17 +5346,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6055,22 +6055,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7492,17 +7492,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8678,17 +8678,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8916,17 +8916,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9400,17 +9400,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -9713,7 +9713,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -10189,7 +10189,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10866,32 +10866,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10899,7 +10903,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10923,17 +10927,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10943,17 +10947,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -11003,12 +11007,12 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -11018,7 +11022,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11057,7 +11061,7 @@
       </c>
       <c r="Z89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA89" s="2" t="inlineStr">
@@ -11100,32 +11104,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11133,7 +11141,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11157,17 +11165,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11177,17 +11185,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -11248,7 +11256,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11330,32 +11338,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11363,7 +11375,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11387,17 +11399,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11407,17 +11419,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -11560,12 +11572,12 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq38推进至seq63，推进25站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -11593,7 +11605,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11601,10 +11613,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q94" s="2" t="inlineStr"/>
-      <c r="R94" s="2" t="inlineStr"/>
-      <c r="S94" s="2" t="inlineStr"/>
-      <c r="T94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>沪南路高科西路</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="S94" s="2" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq25映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U94" s="2" t="inlineStr">
         <is>
           <t>18:12</t>
@@ -11671,32 +11699,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11704,7 +11736,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11728,37 +11760,37 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA95" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -11786,32 +11818,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11819,7 +11855,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11843,17 +11879,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11863,17 +11899,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11970,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12045,7 +12081,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12160,7 +12196,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12275,7 +12311,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12329,7 +12365,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12426,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12505,7 +12541,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12559,7 +12595,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -12620,7 +12656,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12735,7 +12771,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12850,7 +12886,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12965,7 +13001,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13027,22 +13063,22 @@
       <c r="A107" s="2" t="inlineStr"/>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>20:05</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -13075,12 +13111,12 @@
       <c r="M107" s="2" t="inlineStr"/>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13094,47 +13130,392 @@
       <c r="T107" s="2" t="inlineStr"/>
       <c r="U107" s="2" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>21/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
           <t>20:05</t>
         </is>
       </c>
-      <c r="V107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W107" s="2" t="inlineStr">
+      <c r="W108" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X107" s="2" t="inlineStr">
+      <c r="X108" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y107" s="2" t="inlineStr">
+      <c r="Y108" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z107" s="2" t="inlineStr">
+      <c r="Z108" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA107" s="2" t="inlineStr">
+      <c r="AA108" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB107" s="2" t="inlineStr">
+      <c r="AB108" s="2" t="inlineStr">
         <is>
           <t>129.0</t>
         </is>
       </c>
-      <c r="AC107" s="2" t="inlineStr">
+      <c r="AC108" s="2" t="inlineStr">
         <is>
           <t>5/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr"/>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr"/>
+      <c r="R109" s="2" t="inlineStr"/>
+      <c r="S109" s="2" t="inlineStr"/>
+      <c r="T109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V109" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W109" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y109" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z109" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA109" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB109" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC109" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr"/>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr"/>
+      <c r="R110" s="2" t="inlineStr"/>
+      <c r="S110" s="2" t="inlineStr"/>
+      <c r="T110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V110" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W110" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y110" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z110" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA110" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB110" s="2" t="inlineStr">
+        <is>
+          <t>130.7</t>
+        </is>
+      </c>
+      <c r="AC110" s="2" t="inlineStr">
+        <is>
+          <t>9/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-25-浦东35路.xlsx
+++ b/data/export/2026-10-25-浦东35路.xlsx
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2018,17 +2018,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>28/30</t>
+          <t>29/30</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>28/30</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4029,17 +4029,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4989,17 +4989,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5227,17 +5227,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>28/30</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -9172,7 +9172,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9281,17 +9281,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>28/30</t>
+          <t>29/30</t>
         </is>
       </c>
     </row>
@@ -9594,7 +9594,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9638,17 +9638,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -9713,7 +9713,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9995,17 +9995,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10189,7 +10189,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>28/30</t>
         </is>
       </c>
     </row>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -10838,7 +10838,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -10957,7 +10957,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11022,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -11310,7 +11310,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -11544,7 +11544,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11790,7 +11790,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -11828,24 +11828,24 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11855,7 +11855,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -11937,32 +11937,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>17:51</t>
@@ -11970,7 +11974,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11994,17 +11998,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -12014,13 +12018,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB97" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -12081,7 +12089,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12135,7 +12143,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>28/30</t>
+          <t>29/30</t>
         </is>
       </c>
     </row>
@@ -12163,32 +12171,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -12196,7 +12208,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12220,17 +12232,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12240,17 +12252,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -12278,12 +12290,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -12311,7 +12323,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12319,10 +12331,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q100" s="2" t="inlineStr"/>
-      <c r="R100" s="2" t="inlineStr"/>
-      <c r="S100" s="2" t="inlineStr"/>
-      <c r="T100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>19:54</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U100" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -12365,7 +12393,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -12393,32 +12421,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12426,7 +12458,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12450,17 +12482,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12470,17 +12502,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -12508,32 +12540,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12541,7 +12577,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12565,17 +12601,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12585,17 +12621,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -12656,7 +12692,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12738,12 +12774,12 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程51%处后消失；随后反向物理轨迹由seq28推进至seq43，推进15站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -12771,7 +12807,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12779,10 +12815,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q104" s="2" t="inlineStr"/>
-      <c r="R104" s="2" t="inlineStr"/>
-      <c r="S104" s="2" t="inlineStr"/>
-      <c r="T104" s="2" t="inlineStr"/>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>迎春路长柳路</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>20:36</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq33映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 11分钟参与校验</t>
+        </is>
+      </c>
       <c r="U104" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12825,7 +12877,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>28/30</t>
         </is>
       </c>
     </row>
@@ -12886,7 +12938,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -13001,7 +13053,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13116,7 +13168,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13170,7 +13222,7 @@
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -13231,7 +13283,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13285,7 +13337,7 @@
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -13346,7 +13398,7 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
@@ -13400,7 +13452,7 @@
       </c>
       <c r="AC109" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -13461,7 +13513,7 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
@@ -13515,7 +13567,7 @@
       </c>
       <c r="AC110" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
